--- a/jira_export_2026-10-02.xlsx
+++ b/jira_export_2026-10-02.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>26 h</t>
+          <t>32 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2469,7 +2469,7 @@
         <v>3</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
@@ -8146,7 +8146,11 @@
           <t>PDMDEP-35312</t>
         </is>
       </c>
-      <c r="M104" s="15" t="inlineStr"/>
+      <c r="M104" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N104" s="16" t="n">
         <v>450</v>
       </c>
@@ -9067,7 +9071,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -9076,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -9086,7 +9090,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9102,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -9183,22 +9187,22 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>496852</v>
+        <v>499162</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>187236</v>
+        <v>189546</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>309616</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>227420</v>
+        <v>235142</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>29113</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>25777</v>
+        <v>18055</v>
       </c>
     </row>
     <row r="6">
@@ -9208,10 +9212,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>254879</v>
+        <v>257189</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>58241</v>
+        <v>60551</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>196638</v>
@@ -9242,13 +9246,13 @@
         <v>112978</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>50106</v>
+        <v>57828</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>19938</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>18153</v>
+        <v>10431</v>
       </c>
     </row>
   </sheetData>
@@ -9380,7 +9384,7 @@
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="6">
@@ -9401,7 +9405,7 @@
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="7">
@@ -9422,7 +9426,7 @@
         </is>
       </c>
       <c r="I7" s="24" t="n">
-        <v>0</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="8">

--- a/jira_export_2026-10-02.xlsx
+++ b/jira_export_2026-10-02.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>516 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>516 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>32 h</t>
+          <t>43 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1054,27 +1054,27 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35840</t>
+          <t>PDMDEP-35978</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SETE] - Publication des actes</t>
+          <t>[DEPARTEMENT DE LA COTE D'OR (CD 21)] - LiExp - Saas + MV app</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>DEPARTEMENT DE LA COTE D'OR (CD 21)</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Abonnement Publication des actes</t>
+          <t>LiExp - Saas + MV app</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
@@ -1105,16 +1105,16 @@
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35902</t>
+          <t>PDMDEP-35984</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>00182109</t>
+          <t>00182810</t>
         </is>
       </c>
       <c r="N5" s="12" t="n">
-        <v>895</v>
+        <v>2600</v>
       </c>
       <c r="O5" s="13" t="n">
         <v>0</v>
@@ -1126,12 +1126,12 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35782</t>
+          <t>PDMDEP-35883</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Ajout du module Coordination</t>
+          <t>[VILLE DE CHATELLERAULT] - MONTEE DE VERSION LITT EXP test et prod + migration serveur + CONNECTEUR SOGELINK + FLUX WFS COMMUNICATION</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>Ajout du module Coordination</t>
+          <t>MONTEE DE VERSION LITT EXP test et prod + migration serveur + CONNECTEUR SOGELINK + FLUX WFS COMMUNICATION</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -1166,29 +1166,29 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35788</t>
+          <t>PDMDEP-35889</t>
         </is>
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>00181845</t>
+          <t>00182197</t>
         </is>
       </c>
       <c r="N6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="16" t="n">
+        <v>4716</v>
+      </c>
+      <c r="O6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="16" t="n">
@@ -1198,27 +1198,27 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35840</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
+          <t>[COMMUNE DE SETE] - Publication des actes</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
+          <t>Abonnement Publication des actes</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -1238,27 +1238,27 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35902</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00182109</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>3000</v>
+        <v>895</v>
       </c>
       <c r="O7" s="13" t="n">
         <v>0</v>
@@ -1270,32 +1270,32 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35782</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t>[VILLE DE SURESNES] - Ajout du module Coordination</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t>Ajout du module Coordination</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -1305,32 +1305,32 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35788</t>
         </is>
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181845</t>
         </is>
       </c>
       <c r="N8" s="16" t="n">
-        <v>1852.8</v>
+        <v>1412.5</v>
       </c>
       <c r="O8" s="13" t="n">
         <v>0</v>
@@ -1342,12 +1342,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>895</v>
+        <v>3000</v>
       </c>
       <c r="O9" s="13" t="n">
         <v>0</v>
@@ -1414,12 +1414,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
@@ -1465,16 +1465,16 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>4399.5</v>
+        <v>1852.8</v>
       </c>
       <c r="O10" s="13" t="n">
         <v>0</v>
@@ -1486,27 +1486,27 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1526,27 +1526,27 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1470.38</v>
+        <v>805.5</v>
       </c>
       <c r="O11" s="13" t="n">
         <v>0</v>
@@ -1558,27 +1558,27 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Migration V2 (presta)</t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -1609,16 +1609,16 @@
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>2891.501</v>
+        <v>4399.5</v>
       </c>
       <c r="O12" s="13" t="n">
         <v>0</v>
@@ -1630,32 +1630,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1670,27 +1670,27 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>250.5</v>
+        <v>455</v>
       </c>
       <c r="O13" s="13" t="n">
         <v>0</v>
@@ -1702,32 +1702,32 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>1465.2</v>
+        <v>1470.38</v>
       </c>
       <c r="O14" s="13" t="n">
         <v>0</v>
@@ -1774,27 +1774,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1814,27 +1814,27 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>394</v>
+        <v>2891.501</v>
       </c>
       <c r="O15" s="13" t="n">
         <v>0</v>
@@ -1846,32 +1846,32 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
@@ -1897,16 +1897,16 @@
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N16" s="16" t="n">
-        <v>1100</v>
+        <v>250.5</v>
       </c>
       <c r="O16" s="13" t="n">
         <v>0</v>
@@ -1918,32 +1918,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1969,16 +1969,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>960</v>
+        <v>1465.2</v>
       </c>
       <c r="O17" s="13" t="n">
         <v>0</v>
@@ -1990,12 +1990,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2025,32 +2025,32 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>1073.25</v>
+        <v>394</v>
       </c>
       <c r="O18" s="13" t="n">
         <v>0</v>
@@ -2062,27 +2062,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2102,27 +2102,27 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>243.6</v>
+        <v>1100</v>
       </c>
       <c r="O19" s="13" t="n">
         <v>0</v>
@@ -2134,32 +2134,32 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -2169,32 +2169,32 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N20" s="16" t="n">
-        <v>2763.25</v>
+        <v>960</v>
       </c>
       <c r="O20" s="13" t="n">
         <v>0</v>
@@ -2206,12 +2206,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>516</v>
+        <v>1073.25</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>0</v>
@@ -2278,32 +2278,32 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -2329,16 +2329,16 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>1400</v>
+        <v>243.6</v>
       </c>
       <c r="O22" s="13" t="n">
         <v>0</v>
@@ -2350,32 +2350,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2385,34 +2385,34 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="12" t="n">
+        <v>2763.25</v>
+      </c>
+      <c r="O23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2422,12 +2422,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -2473,33 +2473,33 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>1620</v>
-      </c>
-      <c r="O24" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>516</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2545,16 +2545,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>936</v>
+        <v>1400</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2566,12 +2566,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2606,29 +2606,29 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>344</v>
-      </c>
-      <c r="O26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="16" t="n">
@@ -2638,27 +2638,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2673,32 +2673,32 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K27" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>461.7</v>
+        <v>1620</v>
       </c>
       <c r="O27" s="13" t="n">
         <v>0</v>
@@ -2710,27 +2710,27 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -2750,27 +2750,27 @@
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>4150</v>
+        <v>936</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2782,32 +2782,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2817,32 +2817,32 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4254.4</v>
+        <v>344</v>
       </c>
       <c r="O29" s="13" t="n">
         <v>0</v>
@@ -2854,32 +2854,32 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -2905,16 +2905,16 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>2649.6</v>
+        <v>461.7</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
@@ -2926,27 +2926,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>875</v>
+        <v>4150</v>
       </c>
       <c r="O31" s="13" t="n">
         <v>0</v>
@@ -2998,27 +2998,27 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
@@ -3049,16 +3049,16 @@
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>554</v>
+        <v>4254.4</v>
       </c>
       <c r="O32" s="13" t="n">
         <v>0</v>
@@ -3070,32 +3070,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3121,16 +3121,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>9623.1</v>
+        <v>2649.6</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3142,27 +3142,27 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>177.5</v>
+        <v>875</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3214,27 +3214,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3265,16 +3265,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1700</v>
+        <v>554</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3286,27 +3286,27 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE NEUILLY SUR MARNE] - Migration GEODP PLACIER</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP PLACIER</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3337,16 +3337,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>2125</v>
+        <v>9623.1</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3358,12 +3358,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3409,16 +3409,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2696</v>
+        <v>177.5</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3430,27 +3430,27 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>850</v>
+        <v>1700</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3502,32 +3502,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3537,34 +3537,34 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="n">
+        <v>2696</v>
+      </c>
+      <c r="O39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3574,32 +3574,32 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>1980</v>
+        <v>170</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3646,32 +3646,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3718,32 +3718,32 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>136</v>
+        <v>1980</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3790,32 +3790,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3825,32 +3825,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>186.235</v>
+        <v>700</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3862,32 +3862,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -3913,16 +3913,16 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>1890</v>
+        <v>170</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3934,27 +3934,27 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3974,29 +3974,29 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="12" t="n">
+        <v>186.235</v>
+      </c>
+      <c r="O45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
@@ -4006,32 +4006,32 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -4057,16 +4057,16 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>200</v>
+        <v>1890</v>
       </c>
       <c r="O46" s="13" t="n">
         <v>0</v>
@@ -4078,32 +4078,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4113,32 +4113,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4150,32 +4150,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4185,32 +4185,32 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>1221</v>
+        <v>552</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4222,32 +4222,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4262,27 +4262,27 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4294,12 +4294,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
@@ -4345,16 +4345,16 @@
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>8348</v>
+        <v>2000</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4366,12 +4366,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4417,16 +4417,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1032</v>
+        <v>203.5</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4438,32 +4438,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -4489,16 +4489,16 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>240</v>
+        <v>171.4</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4510,32 +4510,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4561,16 +4561,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>149</v>
+        <v>400</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4582,32 +4582,32 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4633,16 +4633,16 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>280</v>
+        <v>6177.52</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4654,32 +4654,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4705,16 +4705,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>680</v>
+        <v>500</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4726,69 +4726,61 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33177</t>
-        </is>
-      </c>
-      <c r="M56" s="15" t="inlineStr">
-        <is>
-          <t>00166356</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L56" s="15" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr"/>
       <c r="N56" s="16" t="n">
-        <v>260</v>
-      </c>
-      <c r="O56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -4798,27 +4790,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4833,12 +4825,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4849,16 +4841,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1047</v>
+        <v>240</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4870,27 +4862,27 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4910,27 +4902,27 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>1618.5</v>
+        <v>149</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4942,12 +4934,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4957,12 +4949,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4982,27 +4974,27 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>400</v>
+        <v>337.5</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -5014,32 +5006,32 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5049,32 +5041,32 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>1400</v>
+        <v>320</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5086,27 +5078,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5121,32 +5113,32 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>305.6</v>
+        <v>1047</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5158,27 +5150,27 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5198,7 +5190,7 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5209,16 +5201,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>2614.5</v>
+        <v>1618.5</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5230,27 +5222,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5270,7 +5262,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5281,16 +5273,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>403.074</v>
+        <v>400</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5302,32 +5294,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5337,12 +5329,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5353,16 +5345,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>142.1</v>
+        <v>200</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5374,27 +5366,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5409,32 +5401,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>6208</v>
+        <v>680.8</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5446,32 +5438,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5481,32 +5473,32 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>1000</v>
+        <v>2614.5</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5518,32 +5510,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5553,32 +5545,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>450</v>
+        <v>403.074</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5590,32 +5582,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5625,32 +5617,32 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>910</v>
+        <v>276</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5662,32 +5654,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5697,32 +5689,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>3240</v>
+        <v>142.1</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5734,12 +5726,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5749,12 +5741,12 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5774,7 +5766,7 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5785,16 +5777,16 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>1050</v>
+        <v>6208</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5806,32 +5798,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5846,7 +5838,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5857,16 +5849,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5878,32 +5870,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5913,12 +5905,12 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
@@ -5929,16 +5921,16 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5950,12 +5942,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5965,12 +5957,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5990,7 +5982,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -6001,16 +5993,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1050</v>
+        <v>450</v>
       </c>
       <c r="O73" s="13" t="n">
         <v>0</v>
@@ -6022,32 +6014,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6057,32 +6049,32 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>203.5</v>
+        <v>910</v>
       </c>
       <c r="O74" s="13" t="n">
         <v>0</v>
@@ -6094,32 +6086,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6129,32 +6121,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1088.5</v>
+        <v>3240</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
@@ -6166,27 +6158,27 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
@@ -6206,27 +6198,27 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>210</v>
+        <v>1050</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6238,12 +6230,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6253,12 +6245,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6278,27 +6270,27 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>130</v>
+        <v>433.5</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6310,12 +6302,12 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -6325,12 +6317,12 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6345,32 +6337,32 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6382,32 +6374,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6417,32 +6409,32 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6454,32 +6446,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6489,32 +6481,32 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
@@ -6526,32 +6518,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6561,32 +6553,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>204.14</v>
+        <v>203.5</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6598,12 +6590,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6613,11 +6605,13 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
@@ -6631,32 +6625,32 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>401.54</v>
+        <v>1088.5</v>
       </c>
       <c r="O82" s="13" t="n">
         <v>0</v>
@@ -6668,32 +6662,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6703,32 +6697,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="O83" s="13" t="n">
         <v>0</v>
@@ -6740,32 +6734,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6775,34 +6769,34 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>210</v>
+      </c>
+      <c r="O84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
@@ -6812,32 +6806,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6847,32 +6841,32 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1790</v>
+        <v>130</v>
       </c>
       <c r="O85" s="13" t="n">
         <v>0</v>
@@ -6884,32 +6878,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6919,34 +6913,34 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="O86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
@@ -6956,32 +6950,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6991,34 +6985,34 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="O87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -7028,12 +7022,12 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -7043,11 +7037,13 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v/>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrage interface Pastell</t>
+        </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
@@ -7066,27 +7062,27 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="O88" s="13" t="n">
         <v>0</v>
@@ -7098,12 +7094,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7113,11 +7109,13 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
@@ -7136,27 +7134,27 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>3016.08</v>
+        <v>204.14</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7168,22 +7166,22 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="E90" s="15" t="n">
@@ -7201,34 +7199,34 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="O90" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
@@ -7238,12 +7236,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7253,11 +7251,13 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
@@ -7276,27 +7276,27 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>3919.06</v>
+        <v>275</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7308,26 +7308,28 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
@@ -7341,34 +7343,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7378,26 +7380,28 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7416,29 +7420,29 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7448,26 +7452,28 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
@@ -7486,23 +7492,23 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
@@ -7518,22 +7524,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
@@ -7548,27 +7554,35 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr"/>
-      <c r="M95" s="11" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7582,22 +7596,22 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E96" s="15" t="n">
@@ -7610,7 +7624,7 @@
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
@@ -7620,21 +7634,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L96" s="15" t="inlineStr"/>
-      <c r="M96" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L96" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M96" s="15" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7644,22 +7666,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7667,7 +7689,7 @@
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7677,32 +7699,32 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>240</v>
+        <v>460</v>
       </c>
       <c r="O97" s="13" t="n">
         <v>0</v>
@@ -7714,12 +7736,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7729,7 +7751,7 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E98" s="15" t="n">
@@ -7752,27 +7774,27 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>557.145</v>
+        <v>3016.08</v>
       </c>
       <c r="O98" s="13" t="n">
         <v>0</v>
@@ -7784,22 +7806,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7812,7 +7834,7 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -7822,21 +7844,29 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="11" t="inlineStr"/>
-      <c r="M99" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27028</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>500950</t>
+        </is>
+      </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7846,22 +7876,22 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E100" s="15" t="n">
@@ -7874,31 +7904,39 @@
       </c>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L100" s="15" t="inlineStr"/>
-      <c r="M100" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L100" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28055</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="inlineStr">
+        <is>
+          <t>499132</t>
+        </is>
+      </c>
       <c r="N100" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O100" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7908,12 +7946,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7923,7 +7961,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7936,39 +7974,39 @@
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7978,12 +8016,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -7993,7 +8031,7 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E102" s="15" t="n">
@@ -8009,32 +8047,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H102" s="15" t="inlineStr"/>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O102" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8044,24 +8086,26 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C103" s="11" t="inlineStr"/>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8070,7 +8114,7 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -8080,17 +8124,25 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8104,21 +8156,27 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr"/>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr"/>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v/>
+      </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8129,32 +8187,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H104" s="15" t="inlineStr"/>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35312</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00177354</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8164,21 +8226,29 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr"/>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr"/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8186,20 +8256,24 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr"/>
       <c r="M105" s="11" t="inlineStr"/>
@@ -8216,21 +8290,27 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="inlineStr"/>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr"/>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v/>
+      </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8238,31 +8318,27 @@
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H106" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K106" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L106" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M106" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+      <c r="L106" s="15" t="inlineStr"/>
+      <c r="M106" s="15" t="inlineStr"/>
       <c r="N106" s="16" t="n">
         <v>0</v>
       </c>
@@ -8276,89 +8352,721 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N107" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J108" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N108" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-15695</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>CD Manche</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>17/06/2024</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="K109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
+      <c r="N109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-13488</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asnieres sur Seine </t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>30/11/2023</t>
+        </is>
+      </c>
+      <c r="J110" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K110" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L110" s="15" t="inlineStr"/>
+      <c r="M110" s="15" t="inlineStr"/>
+      <c r="N110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12666</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H111" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>19/09/2023</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-12292</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="inlineStr"/>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J112" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="K112" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
+      <c r="N112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr"/>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
+      <c r="N113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1339</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr"/>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr"/>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="inlineStr"/>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J114" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1288</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr"/>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr"/>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
+      <c r="N115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr"/>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr"/>
+      <c r="F116" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G116" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="inlineStr"/>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J116" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M116" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
           <t>PSC-1047</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr"/>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr"/>
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr">
+      <c r="E117" s="11" t="inlineStr"/>
+      <c r="F117" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G107" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr"/>
-      <c r="I107" s="11" t="inlineStr">
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr"/>
+      <c r="I117" s="11" t="inlineStr">
         <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J107" s="11" t="n">
+      <c r="J117" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K107" s="11" t="n">
+      <c r="K117" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L107" s="11" t="inlineStr">
+      <c r="L117" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M107" s="11" t="inlineStr">
+      <c r="M117" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="17" t="inlineStr">
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B108" s="17" t="inlineStr"/>
-      <c r="C108" s="17" t="inlineStr"/>
-      <c r="D108" s="17" t="inlineStr"/>
-      <c r="E108" s="17" t="inlineStr"/>
-      <c r="F108" s="17" t="inlineStr"/>
-      <c r="G108" s="17" t="inlineStr"/>
-      <c r="H108" s="17" t="inlineStr"/>
-      <c r="I108" s="17" t="inlineStr"/>
-      <c r="J108" s="17" t="inlineStr"/>
-      <c r="K108" s="17" t="inlineStr"/>
-      <c r="L108" s="17" t="inlineStr"/>
-      <c r="M108" s="17" t="inlineStr"/>
-      <c r="N108" s="18" t="n">
-        <v>114103.655</v>
-      </c>
-      <c r="O108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="18" t="n">
-        <v>0</v>
+      <c r="B118" s="17" t="inlineStr"/>
+      <c r="C118" s="17" t="inlineStr"/>
+      <c r="D118" s="17" t="inlineStr"/>
+      <c r="E118" s="17" t="inlineStr"/>
+      <c r="F118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr"/>
+      <c r="I118" s="17" t="inlineStr"/>
+      <c r="J118" s="17" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr"/>
+      <c r="L118" s="17" t="inlineStr"/>
+      <c r="M118" s="17" t="inlineStr"/>
+      <c r="N118" s="18" t="n">
+        <v>121828.375</v>
+      </c>
+      <c r="O118" s="18" t="n">
+        <v>516</v>
+      </c>
+      <c r="P118" s="18" t="n">
+        <v>16.74</v>
       </c>
     </row>
   </sheetData>
@@ -8467,6 +9175,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8478,18 +9196,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
@@ -8504,7 +9222,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 0 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 2 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -8566,8 +9284,137 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-31812</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE PROVINS</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31819</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>00159472</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="17" t="inlineStr"/>
+      <c r="J7" s="17" t="inlineStr"/>
+      <c r="K7" s="18" t="n">
+        <v>1630</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9041,26 +9888,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>9.75</v>
+        <v>12.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.08</v>
+        <v>0.83</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>18.83</v>
+        <v>22.83</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9949,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9187,10 +10034,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>499162</v>
+        <v>498646</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>189546</v>
+        <v>189030</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>309616</v>
@@ -9237,10 +10084,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>241973</v>
+        <v>241457</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>128995</v>
+        <v>128479</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>112978</v>
@@ -9461,12 +10308,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -9482,7 +10329,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0 clôture(s) : 0 projet(s), 0 rework</t>
+          <t>4 clôture(s) : 4 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -9519,32 +10366,152 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31908</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Commune de GUINGAMP</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>7</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33064</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LONGWY</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34000</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LA GARDE</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34147</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Vaison la romaine</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n">
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-02.xlsx
+++ b/jira_export_2026-10-02.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>43 h</t>
+          <t>50 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1342,32 +1342,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
+          <t xml:space="preserve">[COMMUNE DE BRISSAC LOIRE AUBANCE] - 1/2 journée d'accompagnement a GEODP Placier </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
+          <t xml:space="preserve">1/2 journée d'accompagnement a GEODP Placier </t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
@@ -1393,16 +1393,16 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>3000</v>
+        <v>427.5</v>
       </c>
       <c r="O9" s="13" t="n">
         <v>0</v>
@@ -1414,32 +1414,32 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -1465,16 +1465,16 @@
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1852.8</v>
+        <v>3000</v>
       </c>
       <c r="O10" s="13" t="n">
         <v>0</v>
@@ -1486,32 +1486,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1521,32 +1521,32 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>805.5</v>
+        <v>1852.8</v>
       </c>
       <c r="O11" s="13" t="n">
         <v>0</v>
@@ -1558,32 +1558,32 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -1593,32 +1593,32 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>4399.5</v>
+        <v>805.5</v>
       </c>
       <c r="O12" s="13" t="n">
         <v>0</v>
@@ -1630,32 +1630,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfert de compétence Analyse </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1681,16 +1681,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>455</v>
+        <v>4399.5</v>
       </c>
       <c r="O13" s="13" t="n">
         <v>0</v>
@@ -1702,27 +1702,27 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -1753,16 +1753,16 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35439</t>
+          <t>PDMDEP-35464</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00180506</t>
+          <t>00180631</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>1470.38</v>
+        <v>455</v>
       </c>
       <c r="O14" s="13" t="n">
         <v>0</v>
@@ -1774,69 +1774,61 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35445</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
+          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>COMMUNE DE BOURG EN BRESSE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GeODP - Migration V2 (presta)</t>
+          <t>Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35392</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>00179700</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
       <c r="N15" s="12" t="n">
-        <v>2891.501</v>
-      </c>
-      <c r="O15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1846,32 +1838,32 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -1886,27 +1878,27 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N16" s="16" t="n">
-        <v>250.5</v>
+        <v>1470.38</v>
       </c>
       <c r="O16" s="13" t="n">
         <v>0</v>
@@ -1918,27 +1910,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1958,27 +1950,27 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1465.2</v>
+        <v>5783.002</v>
       </c>
       <c r="O17" s="13" t="n">
         <v>0</v>
@@ -1990,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2030,7 +2022,7 @@
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -2041,16 +2033,16 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>394</v>
+        <v>1053</v>
       </c>
       <c r="O18" s="13" t="n">
         <v>0</v>
@@ -2062,32 +2054,32 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2113,16 +2105,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1100</v>
+        <v>250.5</v>
       </c>
       <c r="O19" s="13" t="n">
         <v>0</v>
@@ -2134,32 +2126,32 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -2169,12 +2161,12 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
@@ -2185,16 +2177,16 @@
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N20" s="16" t="n">
-        <v>960</v>
+        <v>1465.2</v>
       </c>
       <c r="O20" s="13" t="n">
         <v>0</v>
@@ -2206,12 +2198,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2221,12 +2213,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2241,32 +2233,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1073.25</v>
+        <v>394</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>0</v>
@@ -2278,27 +2270,27 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -2318,27 +2310,27 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>243.6</v>
+        <v>1100</v>
       </c>
       <c r="O22" s="13" t="n">
         <v>0</v>
@@ -2350,32 +2342,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2385,32 +2377,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2763.25</v>
+        <v>960</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>0</v>
@@ -2422,12 +2414,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2437,12 +2429,12 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -2457,69 +2449,69 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="16" t="n">
-        <v>516</v>
+        <v>1073.25</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2529,12 +2521,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2545,16 +2537,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1400</v>
+        <v>243.6</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2566,32 +2558,32 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2601,34 +2593,34 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="16" t="n">
+        <v>2763.25</v>
+      </c>
+      <c r="O26" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="16" t="n">
@@ -2638,12 +2630,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2653,12 +2645,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2673,12 +2665,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2689,33 +2681,33 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1620</v>
-      </c>
-      <c r="O27" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="n">
+        <v>516</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2725,12 +2717,12 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -2750,7 +2742,7 @@
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -2761,16 +2753,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>936</v>
+        <v>1400</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2782,12 +2774,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2797,12 +2789,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2822,29 +2814,29 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -2854,27 +2846,27 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
@@ -2889,32 +2881,32 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="K30" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>461.7</v>
+        <v>1620</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
@@ -2926,27 +2918,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2966,27 +2958,27 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>4150</v>
+        <v>936</v>
       </c>
       <c r="O31" s="13" t="n">
         <v>0</v>
@@ -2998,32 +2990,32 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -3033,32 +3025,32 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>4254.4</v>
+        <v>344</v>
       </c>
       <c r="O32" s="13" t="n">
         <v>0</v>
@@ -3070,32 +3062,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3105,12 +3097,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3121,16 +3113,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2649.6</v>
+        <v>153.9</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3142,27 +3134,27 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -3182,7 +3174,7 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3193,16 +3185,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>875</v>
+        <v>4150</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3214,27 +3206,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3249,12 +3241,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3265,16 +3257,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>554</v>
+        <v>2500</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3286,32 +3278,32 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3321,12 +3313,12 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3337,16 +3329,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>9623.1</v>
+        <v>2649.6</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3358,27 +3350,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3398,7 +3390,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3409,16 +3401,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>177.5</v>
+        <v>175</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3430,27 +3422,27 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3465,12 +3457,12 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3481,16 +3473,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>1700</v>
+        <v>775.6</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3502,27 +3494,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3542,7 +3534,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3553,16 +3545,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2696</v>
+        <v>5388.936</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3574,27 +3566,27 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3614,7 +3606,7 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3625,16 +3617,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>170</v>
+        <v>177.5</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3646,32 +3638,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3686,27 +3678,27 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>3000</v>
+        <v>1700</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3718,32 +3710,32 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3753,32 +3745,32 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>1980</v>
+        <v>2696</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3790,27 +3782,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3830,7 +3822,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3841,16 +3833,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3862,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3897,32 +3889,32 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>170</v>
+        <v>3000</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3934,12 +3926,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3949,12 +3941,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3974,27 +3966,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>186.235</v>
+        <v>1980</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>0</v>
@@ -4006,32 +3998,32 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4041,12 +4033,12 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -4057,16 +4049,16 @@
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>1890</v>
+        <v>700</v>
       </c>
       <c r="O46" s="13" t="n">
         <v>0</v>
@@ -4078,32 +4070,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4113,32 +4105,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4150,27 +4142,27 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -4190,27 +4182,27 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>552</v>
+        <v>186.235</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4222,32 +4214,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4262,7 +4254,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4273,16 +4265,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>203.5</v>
+        <v>1890</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4294,32 +4286,32 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4329,32 +4321,32 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4366,32 +4358,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4401,32 +4393,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>203.5</v>
+        <v>552</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4438,32 +4430,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4478,27 +4470,27 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4510,32 +4502,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4545,12 +4537,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4561,16 +4553,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4582,27 +4574,27 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4617,12 +4609,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4633,16 +4625,16 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>6177.52</v>
+        <v>203.5</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4654,32 +4646,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4694,7 +4686,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4705,16 +4697,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>500</v>
+        <v>171.4</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4726,27 +4718,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4756,7 +4748,7 @@
       </c>
       <c r="G56" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H56" s="15" t="inlineStr">
@@ -4766,21 +4758,29 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L56" s="15" t="inlineStr"/>
-      <c r="M56" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33455</t>
+        </is>
+      </c>
+      <c r="M56" s="15" t="inlineStr">
+        <is>
+          <t>00167958</t>
+        </is>
+      </c>
       <c r="N56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="O56" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
@@ -4790,12 +4790,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4841,16 +4841,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>240</v>
+        <v>6177.52</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4862,12 +4862,12 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4913,16 +4913,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4934,27 +4934,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4974,29 +4974,21 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33232</t>
-        </is>
-      </c>
-      <c r="M59" s="11" t="inlineStr">
-        <is>
-          <t>00166708</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
       <c r="N59" s="12" t="n">
-        <v>337.5</v>
-      </c>
-      <c r="O59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -5006,32 +4998,32 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5046,7 +5038,7 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5057,16 +5049,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5078,27 +5070,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5118,7 +5110,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
@@ -5129,16 +5121,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>1047</v>
+        <v>149</v>
       </c>
       <c r="O61" s="13" t="n">
         <v>0</v>
@@ -5150,32 +5142,32 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5185,32 +5177,32 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>1618.5</v>
+        <v>337.5</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5222,12 +5214,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5237,12 +5229,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5262,27 +5254,27 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5294,27 +5286,27 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -5334,27 +5326,27 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>200</v>
+        <v>1047</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5366,32 +5358,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5401,12 +5393,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5417,16 +5409,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>680.8</v>
+        <v>400</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5438,12 +5430,12 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -5453,12 +5445,12 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -5478,7 +5470,7 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
@@ -5489,16 +5481,16 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>2614.5</v>
+        <v>200</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5510,32 +5502,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5545,12 +5537,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5561,16 +5553,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>403.074</v>
+        <v>680.8</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5582,12 +5574,12 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5597,12 +5589,12 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
@@ -5617,12 +5609,12 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
@@ -5633,16 +5625,16 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>276</v>
+        <v>2614.5</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5654,12 +5646,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5669,12 +5661,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5694,7 +5686,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5705,16 +5697,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>142.1</v>
+        <v>403.074</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5726,27 +5718,27 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5761,32 +5753,32 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K70" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>6208</v>
+        <v>276</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5798,12 +5790,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5813,12 +5805,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5838,27 +5830,27 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>1000</v>
+        <v>142.1</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5870,27 +5862,27 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5910,7 +5902,7 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
@@ -5921,16 +5913,16 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>220</v>
+        <v>11278.05</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5942,32 +5934,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5977,12 +5969,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5993,16 +5985,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="O73" s="13" t="n">
         <v>0</v>
@@ -6014,32 +6006,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6049,32 +6041,32 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>910</v>
+        <v>220</v>
       </c>
       <c r="O74" s="13" t="n">
         <v>0</v>
@@ -6086,27 +6078,27 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -6126,7 +6118,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6137,16 +6129,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>3240</v>
+        <v>450</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
@@ -6158,32 +6150,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6193,32 +6185,32 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>1050</v>
+        <v>910</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6230,27 +6222,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6270,7 +6262,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6281,16 +6273,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>433.5</v>
+        <v>3240</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6302,27 +6294,27 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6337,12 +6329,12 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6353,16 +6345,16 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>285</v>
+        <v>1050</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6374,32 +6366,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6409,12 +6401,12 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6425,16 +6417,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>120</v>
+        <v>433.5</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6446,32 +6438,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6481,34 +6473,34 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
@@ -6518,27 +6510,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6553,32 +6545,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>203.5</v>
+        <v>285</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6590,12 +6582,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6605,12 +6597,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6630,27 +6622,27 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>1088.5</v>
+        <v>120</v>
       </c>
       <c r="O82" s="13" t="n">
         <v>0</v>
@@ -6662,12 +6654,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6677,12 +6669,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6702,27 +6694,27 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O83" s="13" t="n">
         <v>0</v>
@@ -6734,27 +6726,27 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6769,12 +6761,12 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
@@ -6785,16 +6777,16 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>210</v>
+        <v>203.5</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
@@ -6806,32 +6798,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6841,12 +6833,12 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6857,16 +6849,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O85" s="13" t="n">
         <v>0</v>
@@ -6878,12 +6870,12 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -6893,12 +6885,12 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6918,7 +6910,7 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6929,16 +6921,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O86" s="13" t="n">
         <v>0</v>
@@ -6950,12 +6942,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6965,12 +6957,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6990,27 +6982,27 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="O87" s="13" t="n">
         <v>0</v>
@@ -7022,32 +7014,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7057,32 +7049,32 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="O88" s="13" t="n">
         <v>0</v>
@@ -7094,32 +7086,32 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
@@ -7129,32 +7121,32 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>204.14</v>
+        <v>255</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7166,30 +7158,32 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE ALENCON</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>Migration 1 activité GEODP2</t>
+        </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7199,32 +7193,32 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>401.54</v>
+        <v>140</v>
       </c>
       <c r="O90" s="13" t="n">
         <v>0</v>
@@ -7236,12 +7230,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7251,12 +7245,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7271,32 +7265,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7308,27 +7302,27 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7343,34 +7337,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O92" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7380,12 +7374,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7395,13 +7389,11 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v/>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7415,34 +7407,34 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7452,12 +7444,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7467,13 +7459,11 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v/>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
@@ -7492,29 +7482,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="O94" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7575,18 +7565,18 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7596,12 +7586,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7611,11 +7601,13 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
@@ -7634,29 +7626,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7666,12 +7658,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7681,11 +7673,13 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7699,32 +7693,32 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>460</v>
+        <v>1790</v>
       </c>
       <c r="O97" s="13" t="n">
         <v>0</v>
@@ -7736,26 +7730,28 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
@@ -7769,34 +7765,34 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>3016.08</v>
-      </c>
-      <c r="O98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7806,26 +7802,28 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7839,34 +7837,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7876,12 +7874,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7891,7 +7889,7 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E100" s="15" t="n">
@@ -7914,27 +7912,27 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>3919.06</v>
+        <v>1000</v>
       </c>
       <c r="O100" s="13" t="n">
         <v>0</v>
@@ -7946,12 +7944,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7961,7 +7959,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7984,27 +7982,27 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>250</v>
+        <v>460</v>
       </c>
       <c r="O101" s="13" t="n">
         <v>0</v>
@@ -8016,12 +8014,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8031,7 +8029,7 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E102" s="15" t="n">
@@ -8054,27 +8052,27 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>230</v>
+        <v>3016.08</v>
       </c>
       <c r="O102" s="13" t="n">
         <v>0</v>
@@ -8086,12 +8084,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8101,7 +8099,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8119,34 +8117,34 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>0.25</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8156,22 +8154,22 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E104" s="15" t="n">
@@ -8194,29 +8192,29 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O104" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8226,28 +8224,26 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>MONTREUIL</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v/>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8256,7 +8252,7 @@
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -8266,21 +8262,29 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L105" s="11" t="inlineStr"/>
-      <c r="M105" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O105" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8290,12 +8294,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8305,7 +8309,7 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8318,31 +8322,39 @@
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L106" s="15" t="inlineStr"/>
-      <c r="M106" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M106" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N106" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O106" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="16" t="n">
@@ -8352,22 +8364,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8375,7 +8387,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8385,34 +8397,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8422,12 +8434,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8437,7 +8449,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8455,34 +8467,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8492,26 +8504,28 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8530,14 +8544,14 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L109" s="11" t="inlineStr"/>
       <c r="M109" s="11" t="inlineStr"/>
@@ -8554,12 +8568,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8569,7 +8583,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8587,19 +8601,19 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -8616,22 +8630,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8639,44 +8653,44 @@
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8686,12 +8700,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8701,7 +8715,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8717,32 +8731,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H112" s="15" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O112" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8752,24 +8770,26 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr"/>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD Manche</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v/>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8783,19 +8803,19 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8812,21 +8832,27 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C114" s="15" t="inlineStr"/>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr"/>
+          <t xml:space="preserve">Asnieres sur Seine </t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v/>
+      </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8834,35 +8860,31 @@
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M114" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr"/>
+      <c r="M114" s="15" t="inlineStr"/>
       <c r="N114" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8872,21 +8894,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr"/>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v/>
+      </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8894,23 +8922,35 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H115" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr"/>
-      <c r="M115" s="11" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8924,21 +8964,27 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v/>
+      </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8952,23 +8998,23 @@
       <c r="H116" s="15" t="inlineStr"/>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -8984,89 +9030,321 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr"/>
       <c r="D117" s="11" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="K117" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1339</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr"/>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr"/>
+      <c r="F118" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G118" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="inlineStr"/>
+      <c r="I118" s="15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J118" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M118" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
+      <c r="N118" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O118" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1288</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr"/>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr"/>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr"/>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
+      <c r="N119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr"/>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr"/>
+      <c r="F120" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr"/>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J120" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K120" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
           <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr"/>
-      <c r="F117" s="11" t="inlineStr">
+      <c r="C121" s="11" t="inlineStr"/>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G117" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr"/>
-      <c r="I117" s="11" t="inlineStr">
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr"/>
+      <c r="I121" s="11" t="inlineStr">
         <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J117" s="11" t="n">
+      <c r="J121" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K117" s="11" t="n">
+      <c r="K121" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L117" s="11" t="inlineStr">
+      <c r="L121" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M117" s="11" t="inlineStr">
+      <c r="M121" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
+      <c r="N121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B118" s="17" t="inlineStr"/>
-      <c r="C118" s="17" t="inlineStr"/>
-      <c r="D118" s="17" t="inlineStr"/>
-      <c r="E118" s="17" t="inlineStr"/>
-      <c r="F118" s="17" t="inlineStr"/>
-      <c r="G118" s="17" t="inlineStr"/>
-      <c r="H118" s="17" t="inlineStr"/>
-      <c r="I118" s="17" t="inlineStr"/>
-      <c r="J118" s="17" t="inlineStr"/>
-      <c r="K118" s="17" t="inlineStr"/>
-      <c r="L118" s="17" t="inlineStr"/>
-      <c r="M118" s="17" t="inlineStr"/>
-      <c r="N118" s="18" t="n">
-        <v>121828.375</v>
-      </c>
-      <c r="O118" s="18" t="n">
+      <c r="B122" s="17" t="inlineStr"/>
+      <c r="C122" s="17" t="inlineStr"/>
+      <c r="D122" s="17" t="inlineStr"/>
+      <c r="E122" s="17" t="inlineStr"/>
+      <c r="F122" s="17" t="inlineStr"/>
+      <c r="G122" s="17" t="inlineStr"/>
+      <c r="H122" s="17" t="inlineStr"/>
+      <c r="I122" s="17" t="inlineStr"/>
+      <c r="J122" s="17" t="inlineStr"/>
+      <c r="K122" s="17" t="inlineStr"/>
+      <c r="L122" s="17" t="inlineStr"/>
+      <c r="M122" s="17" t="inlineStr"/>
+      <c r="N122" s="18" t="n">
+        <v>122877.162</v>
+      </c>
+      <c r="O122" s="18" t="n">
         <v>516</v>
       </c>
-      <c r="P118" s="18" t="n">
-        <v>16.74</v>
+      <c r="P122" s="18" t="n">
+        <v>15.03</v>
       </c>
     </row>
   </sheetData>
@@ -9185,6 +9463,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9888,26 +10170,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>12.75</v>
+        <v>16</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>9.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>22.83</v>
+        <v>26.33</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
     </row>
@@ -9949,7 +10231,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
